--- a/web/files/港岛-半山区西部-大学阁.xlsx
+++ b/web/files/港岛-半山区西部-大学阁.xlsx
@@ -756,7 +756,7 @@
         </is>
       </c>
       <c r="E3" s="4" t="n">
-        <v>3160</v>
+        <v>3147</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -772,7 +772,7 @@
         <v>258054000</v>
       </c>
       <c r="I3" s="5" t="n">
-        <v>81663</v>
+        <v>82000</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
@@ -822,7 +822,7 @@
         </is>
       </c>
       <c r="E4" s="4" t="n">
-        <v>1505</v>
+        <v>1584</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         <v>91872000</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>61045</v>
+        <v>58000</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         </is>
       </c>
       <c r="E5" s="4" t="n">
-        <v>1507</v>
+        <v>1587</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         <v>95220000</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>63185</v>
+        <v>60000</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="E6" s="4" t="n">
-        <v>1506</v>
+        <v>1584</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -970,7 +970,7 @@
         <v>79000000</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>52457</v>
+        <v>49874</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         </is>
       </c>
       <c r="E7" s="4" t="n">
-        <v>1506</v>
+        <v>1584</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
@@ -1036,7 +1036,7 @@
         <v>82000000</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>54449</v>
+        <v>51768</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         </is>
       </c>
       <c r="E8" s="4" t="n">
-        <v>1506</v>
+        <v>1584</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>81000000</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>53785</v>
+        <v>51136</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
         </is>
       </c>
       <c r="E9" s="4" t="n">
-        <v>1506</v>
+        <v>1584</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>86330000</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>57324</v>
+        <v>54501</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         </is>
       </c>
       <c r="E10" s="4" t="n">
-        <v>1508</v>
+        <v>1584</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
@@ -1234,7 +1234,7 @@
         <v>76800000</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>50928</v>
+        <v>48485</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         </is>
       </c>
       <c r="E12" s="4" t="n">
-        <v>1508</v>
+        <v>1584</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         <v>77299200</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>51259</v>
+        <v>48800</v>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         </is>
       </c>
       <c r="E13" s="4" t="n">
-        <v>1547</v>
+        <v>1584</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>80100000</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>51778</v>
+        <v>50568</v>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
@@ -1482,7 +1482,7 @@
         </is>
       </c>
       <c r="E14" s="4" t="n">
-        <v>1508</v>
+        <v>1584</v>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
@@ -1498,7 +1498,7 @@
         <v>66000000</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>43767</v>
+        <v>41667</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
@@ -1548,7 +1548,7 @@
         </is>
       </c>
       <c r="E15" s="4" t="n">
-        <v>1547</v>
+        <v>1584</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>73000000</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>47188</v>
+        <v>46086</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
@@ -1614,7 +1614,7 @@
         </is>
       </c>
       <c r="E16" s="4" t="n">
-        <v>1547</v>
+        <v>1584</v>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
@@ -1630,7 +1630,7 @@
         <v>68800000</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>44473</v>
+        <v>43434</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
@@ -1680,7 +1680,7 @@
         </is>
       </c>
       <c r="E17" s="4" t="n">
-        <v>1508</v>
+        <v>1584</v>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>65000000</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>43103</v>
+        <v>41035</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
         </is>
       </c>
       <c r="E18" s="4" t="n">
-        <v>1508</v>
+        <v>1584</v>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
         <v>69500000</v>
       </c>
       <c r="I18" s="5" t="n">
-        <v>46088</v>
+        <v>43876</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         </is>
       </c>
       <c r="E19" s="4" t="n">
-        <v>1508</v>
+        <v>1584</v>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
@@ -1828,7 +1828,7 @@
         <v>71800000</v>
       </c>
       <c r="I19" s="5" t="n">
-        <v>47613</v>
+        <v>45328</v>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
@@ -1878,7 +1878,7 @@
         </is>
       </c>
       <c r="E20" s="4" t="n">
-        <v>1508</v>
+        <v>1584</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
@@ -1894,7 +1894,7 @@
         <v>60000000</v>
       </c>
       <c r="I20" s="5" t="n">
-        <v>39788</v>
+        <v>37879</v>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         </is>
       </c>
       <c r="E21" s="4" t="n">
-        <v>1508</v>
+        <v>1584</v>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
@@ -1960,7 +1960,7 @@
         <v>66000000</v>
       </c>
       <c r="I21" s="5" t="n">
-        <v>43767</v>
+        <v>41667</v>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
@@ -2010,7 +2010,7 @@
         </is>
       </c>
       <c r="E22" s="4" t="n">
-        <v>1508</v>
+        <v>1584</v>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
@@ -2026,7 +2026,7 @@
         <v>65000000</v>
       </c>
       <c r="I22" s="5" t="n">
-        <v>43103</v>
+        <v>41035</v>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
@@ -2076,7 +2076,7 @@
         </is>
       </c>
       <c r="E23" s="4" t="n">
-        <v>1508</v>
+        <v>1584</v>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
@@ -2092,7 +2092,7 @@
         <v>68000000</v>
       </c>
       <c r="I23" s="5" t="n">
-        <v>45093</v>
+        <v>42929</v>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
@@ -2142,7 +2142,7 @@
         </is>
       </c>
       <c r="E24" s="4" t="n">
-        <v>1508</v>
+        <v>1584</v>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
@@ -2158,7 +2158,7 @@
         <v>58800000</v>
       </c>
       <c r="I24" s="5" t="n">
-        <v>38992</v>
+        <v>37121</v>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
@@ -2208,7 +2208,7 @@
         </is>
       </c>
       <c r="E25" s="4" t="n">
-        <v>1508</v>
+        <v>1584</v>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
@@ -2224,7 +2224,7 @@
         <v>63680000</v>
       </c>
       <c r="I25" s="5" t="n">
-        <v>42228</v>
+        <v>40202</v>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
@@ -2274,7 +2274,7 @@
         </is>
       </c>
       <c r="E26" s="4" t="n">
-        <v>1438</v>
+        <v>1515</v>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
@@ -2290,7 +2290,7 @@
         <v>65000000</v>
       </c>
       <c r="I26" s="5" t="n">
-        <v>45202</v>
+        <v>42904</v>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
@@ -2340,7 +2340,7 @@
         </is>
       </c>
       <c r="E27" s="4" t="n">
-        <v>1475</v>
+        <v>1515</v>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
@@ -2356,7 +2356,7 @@
         <v>68000000</v>
       </c>
       <c r="I27" s="5" t="n">
-        <v>46102</v>
+        <v>44884</v>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
@@ -2406,7 +2406,7 @@
         </is>
       </c>
       <c r="E28" s="4" t="n">
-        <v>3154</v>
+        <v>3237</v>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
@@ -2422,7 +2422,7 @@
         <v>254300000</v>
       </c>
       <c r="I28" s="5" t="n">
-        <v>80628</v>
+        <v>78560</v>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
@@ -2472,7 +2472,7 @@
         </is>
       </c>
       <c r="E29" s="4" t="n">
-        <v>1505</v>
+        <v>1584</v>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
@@ -2488,7 +2488,7 @@
         <v>80408000</v>
       </c>
       <c r="I29" s="5" t="n">
-        <v>53427</v>
+        <v>50763</v>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         </is>
       </c>
       <c r="E30" s="4" t="n">
-        <v>1507</v>
+        <v>1587</v>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
@@ -2554,7 +2554,7 @@
         <v>83880000</v>
       </c>
       <c r="I30" s="5" t="n">
-        <v>55660</v>
+        <v>52854</v>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
         </is>
       </c>
       <c r="E31" s="4" t="n">
-        <v>1506</v>
+        <v>1584</v>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
@@ -2620,7 +2620,7 @@
         <v>78000000</v>
       </c>
       <c r="I31" s="5" t="n">
-        <v>51793</v>
+        <v>49242</v>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
@@ -2670,7 +2670,7 @@
         </is>
       </c>
       <c r="E32" s="4" t="n">
-        <v>1506</v>
+        <v>1584</v>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
@@ -2686,7 +2686,7 @@
         <v>79500000</v>
       </c>
       <c r="I32" s="5" t="n">
-        <v>52789</v>
+        <v>50189</v>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
         </is>
       </c>
       <c r="E33" s="4" t="n">
-        <v>1506</v>
+        <v>1584</v>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
@@ -2752,7 +2752,7 @@
         <v>74000000</v>
       </c>
       <c r="I33" s="5" t="n">
-        <v>49137</v>
+        <v>46717</v>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
         </is>
       </c>
       <c r="E34" s="4" t="n">
-        <v>1506</v>
+        <v>1584</v>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
@@ -2818,7 +2818,7 @@
         <v>76000000</v>
       </c>
       <c r="I34" s="5" t="n">
-        <v>50465</v>
+        <v>47980</v>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
         </is>
       </c>
       <c r="E35" s="4" t="n">
-        <v>1508</v>
+        <v>1584</v>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
@@ -2884,7 +2884,7 @@
         <v>68800000</v>
       </c>
       <c r="I35" s="5" t="n">
-        <v>45623</v>
+        <v>43434</v>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
@@ -2934,7 +2934,7 @@
         </is>
       </c>
       <c r="E36" s="4" t="n">
-        <v>1508</v>
+        <v>1584</v>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
@@ -2950,7 +2950,7 @@
         <v>69500000</v>
       </c>
       <c r="I36" s="5" t="n">
-        <v>46088</v>
+        <v>43876</v>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
@@ -3000,7 +3000,7 @@
         </is>
       </c>
       <c r="E37" s="4" t="n">
-        <v>1508</v>
+        <v>1584</v>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
@@ -3016,7 +3016,7 @@
         <v>72000000</v>
       </c>
       <c r="I37" s="5" t="n">
-        <v>47745</v>
+        <v>45455</v>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
@@ -3066,7 +3066,7 @@
         </is>
       </c>
       <c r="E38" s="4" t="n">
-        <v>1508</v>
+        <v>1584</v>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
@@ -3082,7 +3082,7 @@
         <v>73980000</v>
       </c>
       <c r="I38" s="5" t="n">
-        <v>49058</v>
+        <v>46705</v>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
@@ -3198,7 +3198,7 @@
         </is>
       </c>
       <c r="E40" s="4" t="n">
-        <v>1508</v>
+        <v>1584</v>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
@@ -3214,7 +3214,7 @@
         <v>67500000</v>
       </c>
       <c r="I40" s="5" t="n">
-        <v>44761</v>
+        <v>42614</v>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
         </is>
       </c>
       <c r="E41" s="4" t="n">
-        <v>1508</v>
+        <v>1584</v>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
@@ -3280,7 +3280,7 @@
         <v>68500000</v>
       </c>
       <c r="I41" s="5" t="n">
-        <v>45424</v>
+        <v>43245</v>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
@@ -3330,7 +3330,7 @@
         </is>
       </c>
       <c r="E42" s="4" t="n">
-        <v>1508</v>
+        <v>1584</v>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
@@ -3346,7 +3346,7 @@
         <v>65000000</v>
       </c>
       <c r="I42" s="5" t="n">
-        <v>43103</v>
+        <v>41035</v>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
         </is>
       </c>
       <c r="E43" s="4" t="n">
-        <v>1508</v>
+        <v>1584</v>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
@@ -3412,7 +3412,7 @@
         <v>62600000</v>
       </c>
       <c r="I43" s="5" t="n">
-        <v>41512</v>
+        <v>39520</v>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
@@ -3462,7 +3462,7 @@
         </is>
       </c>
       <c r="E44" s="4" t="n">
-        <v>1508</v>
+        <v>1584</v>
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
@@ -3478,7 +3478,7 @@
         <v>63400000</v>
       </c>
       <c r="I44" s="5" t="n">
-        <v>42042</v>
+        <v>40025</v>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
@@ -3528,7 +3528,7 @@
         </is>
       </c>
       <c r="E45" s="4" t="n">
-        <v>1508</v>
+        <v>1584</v>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
@@ -3544,7 +3544,7 @@
         <v>61800000</v>
       </c>
       <c r="I45" s="5" t="n">
-        <v>40981</v>
+        <v>39015</v>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
@@ -3594,7 +3594,7 @@
         </is>
       </c>
       <c r="E46" s="4" t="n">
-        <v>1508</v>
+        <v>1584</v>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
@@ -3610,7 +3610,7 @@
         <v>62500000</v>
       </c>
       <c r="I46" s="5" t="n">
-        <v>41446</v>
+        <v>39457</v>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
@@ -3660,7 +3660,7 @@
         </is>
       </c>
       <c r="E47" s="4" t="n">
-        <v>1508</v>
+        <v>1584</v>
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
@@ -3676,7 +3676,7 @@
         <v>64800000</v>
       </c>
       <c r="I47" s="5" t="n">
-        <v>42971</v>
+        <v>40909</v>
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
@@ -3726,7 +3726,7 @@
         </is>
       </c>
       <c r="E48" s="4" t="n">
-        <v>1508</v>
+        <v>1584</v>
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
@@ -3742,7 +3742,7 @@
         <v>61200000</v>
       </c>
       <c r="I48" s="5" t="n">
-        <v>40584</v>
+        <v>38636</v>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
@@ -3792,7 +3792,7 @@
         </is>
       </c>
       <c r="E49" s="4" t="n">
-        <v>1508</v>
+        <v>1584</v>
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
@@ -3808,7 +3808,7 @@
         <v>62000000</v>
       </c>
       <c r="I49" s="5" t="n">
-        <v>41114</v>
+        <v>39141</v>
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
@@ -3858,7 +3858,7 @@
         </is>
       </c>
       <c r="E50" s="4" t="n">
-        <v>1508</v>
+        <v>1584</v>
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
@@ -3874,7 +3874,7 @@
         <v>62800000</v>
       </c>
       <c r="I50" s="5" t="n">
-        <v>41645</v>
+        <v>39646</v>
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
@@ -3924,7 +3924,7 @@
         </is>
       </c>
       <c r="E51" s="4" t="n">
-        <v>1438</v>
+        <v>1515</v>
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
@@ -3940,7 +3940,7 @@
         <v>64500000</v>
       </c>
       <c r="I51" s="5" t="n">
-        <v>44854</v>
+        <v>42574</v>
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
@@ -3990,7 +3990,7 @@
         </is>
       </c>
       <c r="E52" s="4" t="n">
-        <v>1438</v>
+        <v>1515</v>
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
@@ -4006,7 +4006,7 @@
         <v>65800000</v>
       </c>
       <c r="I52" s="5" t="n">
-        <v>45758</v>
+        <v>43432</v>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
@@ -4126,7 +4126,7 @@
         </is>
       </c>
       <c r="E54" s="4" t="n">
-        <v>1505</v>
+        <v>1584</v>
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
@@ -4196,7 +4196,7 @@
         </is>
       </c>
       <c r="E55" s="4" t="n">
-        <v>1507</v>
+        <v>1587</v>
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
@@ -4266,7 +4266,7 @@
         </is>
       </c>
       <c r="E56" s="4" t="n">
-        <v>1506</v>
+        <v>1584</v>
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
@@ -4336,7 +4336,7 @@
         </is>
       </c>
       <c r="E57" s="4" t="n">
-        <v>1547</v>
+        <v>1584</v>
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
@@ -4406,7 +4406,7 @@
         </is>
       </c>
       <c r="E58" s="4" t="n">
-        <v>1506</v>
+        <v>1584</v>
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
@@ -4476,7 +4476,7 @@
         </is>
       </c>
       <c r="E59" s="4" t="n">
-        <v>1506</v>
+        <v>1584</v>
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
@@ -4546,7 +4546,7 @@
         </is>
       </c>
       <c r="E60" s="4" t="n">
-        <v>1508</v>
+        <v>1584</v>
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
@@ -4616,7 +4616,7 @@
         </is>
       </c>
       <c r="E61" s="4" t="n">
-        <v>1508</v>
+        <v>1584</v>
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
@@ -4966,7 +4966,7 @@
         </is>
       </c>
       <c r="E66" s="4" t="n">
-        <v>1508</v>
+        <v>1584</v>
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
@@ -5036,7 +5036,7 @@
         </is>
       </c>
       <c r="E67" s="4" t="n">
-        <v>1508</v>
+        <v>1584</v>
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
@@ -5106,7 +5106,7 @@
         </is>
       </c>
       <c r="E68" s="4" t="n">
-        <v>1508</v>
+        <v>1584</v>
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
@@ -5176,7 +5176,7 @@
         </is>
       </c>
       <c r="E69" s="4" t="n">
-        <v>1508</v>
+        <v>1584</v>
       </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
@@ -5246,7 +5246,7 @@
         </is>
       </c>
       <c r="E70" s="4" t="n">
-        <v>1508</v>
+        <v>1584</v>
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
@@ -5386,7 +5386,7 @@
         </is>
       </c>
       <c r="E72" s="4" t="n">
-        <v>1508</v>
+        <v>1584</v>
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
@@ -5456,7 +5456,7 @@
         </is>
       </c>
       <c r="E73" s="4" t="n">
-        <v>1508</v>
+        <v>1584</v>
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
@@ -5526,7 +5526,7 @@
         </is>
       </c>
       <c r="E74" s="4" t="n">
-        <v>1508</v>
+        <v>1584</v>
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
@@ -5596,7 +5596,7 @@
         </is>
       </c>
       <c r="E75" s="4" t="n">
-        <v>1508</v>
+        <v>1584</v>
       </c>
       <c r="F75" s="3" t="inlineStr">
         <is>
@@ -5666,7 +5666,7 @@
         </is>
       </c>
       <c r="E76" s="4" t="n">
-        <v>1438</v>
+        <v>1515</v>
       </c>
       <c r="F76" s="3" t="inlineStr">
         <is>
@@ -5682,7 +5682,7 @@
         <v>64000000</v>
       </c>
       <c r="I76" s="5" t="n">
-        <v>44506</v>
+        <v>42244</v>
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
@@ -5732,7 +5732,7 @@
         </is>
       </c>
       <c r="E77" s="4" t="n">
-        <v>1438</v>
+        <v>1515</v>
       </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
@@ -5748,7 +5748,7 @@
         <v>64500000</v>
       </c>
       <c r="I77" s="5" t="n">
-        <v>44854</v>
+        <v>42574</v>
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
@@ -5895,9 +5895,9 @@
       </c>
       <c r="B5" s="20" t="inlineStr">
         <is>
-          <t>A | 3160呎 (4+房)
+          <t>A | 3147呎 (4+房)
 $25805万
-$81,663/呎
+$82,000/呎
 (22年-01月-19日)</t>
         </is>
       </c>
@@ -5911,17 +5911,17 @@
       </c>
       <c r="B6" s="20" t="inlineStr">
         <is>
-          <t>A | 1507呎 (4+房)
+          <t>A | 1587呎 (4+房)
 $9522万
-$63,185/呎
+$60,000/呎
 (22年-01月-19日)</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
         <is>
-          <t>B | 1505呎 (4+房)
+          <t>B | 1584呎 (4+房)
 $9187万
-$61,045/呎
+$58,000/呎
 (22年-01月-19日)</t>
         </is>
       </c>
@@ -5934,17 +5934,17 @@
       </c>
       <c r="B7" s="20" t="inlineStr">
         <is>
-          <t>A | 1506呎 (4+房)
+          <t>A | 1584呎 (4+房)
 $8200万
-$54,449/呎
+$51,768/呎
 (23年-07月-06日)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
         <is>
-          <t>B | 1506呎 (4+房)
+          <t>B | 1584呎 (4+房)
 $7900万
-$52,457/呎
+$49,874/呎
 (25年-05月-20日)</t>
         </is>
       </c>
@@ -5957,17 +5957,17 @@
       </c>
       <c r="B8" s="20" t="inlineStr">
         <is>
-          <t>A | 1506呎 (3房)
+          <t>A | 1584呎 (3房)
 $8633万
-$57,324/呎
+$54,501/呎
 (23年-02月-24日)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
         <is>
-          <t>B | 1506呎 (4+房)
+          <t>B | 1584呎 (4+房)
 $8100万
-$53,785/呎
+$51,136/呎
 (23年-06月-12日)</t>
         </is>
       </c>
@@ -5988,9 +5988,9 @@
       </c>
       <c r="C9" s="20" t="inlineStr">
         <is>
-          <t>B | 1508呎 (4+房)
+          <t>B | 1584呎 (4+房)
 $7680万
-$50,928/呎
+$48,485/呎
 (23年-02月-06日)</t>
         </is>
       </c>
@@ -6003,17 +6003,17 @@
       </c>
       <c r="B10" s="20" t="inlineStr">
         <is>
-          <t>A | 1547呎 (4+房)
+          <t>A | 1584呎 (4+房)
 $8010万
-$51,778/呎
+$50,568/呎
 (21年-11月-10日)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
         <is>
-          <t>B | 1508呎 (4+房)
+          <t>B | 1584呎 (4+房)
 $7730万
-$51,259/呎
+$48,800/呎
 (22年-01月-13日)</t>
         </is>
       </c>
@@ -6026,17 +6026,17 @@
       </c>
       <c r="B11" s="20" t="inlineStr">
         <is>
-          <t>A | 1547呎 (4+房)
+          <t>A | 1584呎 (4+房)
 $7300万
-$47,188/呎
+$46,086/呎
 (22年-12月-05日)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
         <is>
-          <t>B | 1508呎 (4+房)
+          <t>B | 1584呎 (4+房)
 $6600万
-$43,767/呎
+$41,667/呎
 (23年-07月-25日)</t>
         </is>
       </c>
@@ -6049,17 +6049,17 @@
       </c>
       <c r="B12" s="20" t="inlineStr">
         <is>
-          <t>A | 1508呎 (4+房)
+          <t>A | 1584呎 (4+房)
 $6500万
-$43,103/呎
+$41,035/呎
 (22年-12月-30日)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
         <is>
-          <t>B | 1547呎 (4+房)
+          <t>B | 1584呎 (4+房)
 $6880万
-$44,473/呎
+$43,434/呎
 (22年-12月-07日)</t>
         </is>
       </c>
@@ -6072,17 +6072,17 @@
       </c>
       <c r="B13" s="20" t="inlineStr">
         <is>
-          <t>A | 1508呎 (4+房)
+          <t>A | 1584呎 (4+房)
 $7180万
-$47,613/呎
+$45,328/呎
 (22年-07月-14日)</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
         <is>
-          <t>B | 1508呎 (4+房)
+          <t>B | 1584呎 (4+房)
 $6950万
-$46,088/呎
+$43,876/呎
 (22年-02月-17日)</t>
         </is>
       </c>
@@ -6095,17 +6095,17 @@
       </c>
       <c r="B14" s="20" t="inlineStr">
         <is>
-          <t>A | 1508呎 (3房)
+          <t>A | 1584呎 (3房)
 $6600万
-$43,767/呎
+$41,667/呎
 (23年-01月-06日)</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
         <is>
-          <t>B | 1508呎 (3房)
+          <t>B | 1584呎 (3房)
 $6000万
-$39,788/呎
+$37,879/呎
 (22年-10月-24日)</t>
         </is>
       </c>
@@ -6118,17 +6118,17 @@
       </c>
       <c r="B15" s="20" t="inlineStr">
         <is>
-          <t>A | 1508呎 (3房)
+          <t>A | 1584呎 (3房)
 $6800万
-$45,093/呎
+$42,929/呎
 (22年-05月-03日)</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
         <is>
-          <t>B | 1508呎 (3房)
+          <t>B | 1584呎 (3房)
 $6500万
-$43,103/呎
+$41,035/呎
 (22年-05月-16日)</t>
         </is>
       </c>
@@ -6141,17 +6141,17 @@
       </c>
       <c r="B16" s="20" t="inlineStr">
         <is>
-          <t>A | 1508呎 (3房)
+          <t>A | 1584呎 (3房)
 $6368万
-$42,228/呎
+$40,202/呎
 (23年-02月-02日)</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
         <is>
-          <t>B | 1508呎 (3房)
+          <t>B | 1584呎 (3房)
 $5880万
-$38,992/呎
+$37,121/呎
 (22年-05月-03日)</t>
         </is>
       </c>
@@ -6164,17 +6164,17 @@
       </c>
       <c r="B17" s="20" t="inlineStr">
         <is>
-          <t>A | 1475呎 (3房)
+          <t>A | 1515呎 (3房)
 $6800万
-$46,102/呎
+$44,884/呎
 (23年-02月-16日)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
         <is>
-          <t>B | 1438呎 (3房)
+          <t>B | 1515呎 (3房)
 $6500万
-$45,202/呎
+$42,904/呎
 (23年-01月-17日)</t>
         </is>
       </c>
@@ -6298,9 +6298,9 @@
       </c>
       <c r="B5" s="20" t="inlineStr">
         <is>
-          <t>A | 3154呎 (4+房)
+          <t>A | 3237呎 (4+房)
 $25430万
-$80,628/呎
+$78,560/呎
 (23年-11月-22日)</t>
         </is>
       </c>
@@ -6314,17 +6314,17 @@
       </c>
       <c r="B6" s="20" t="inlineStr">
         <is>
-          <t>A | 1507呎 (4+房)
+          <t>A | 1587呎 (4+房)
 $8388万
-$55,660/呎
+$52,854/呎
 (25年-11月-10日)</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
         <is>
-          <t>B | 1505呎 (4+房)
+          <t>B | 1584呎 (4+房)
 $8041万
-$53,427/呎
+$50,763/呎
 (25年-11月-10日)</t>
         </is>
       </c>
@@ -6337,17 +6337,17 @@
       </c>
       <c r="B7" s="20" t="inlineStr">
         <is>
-          <t>A | 1506呎 (4+房)
+          <t>A | 1584呎 (4+房)
 $7950万
-$52,789/呎
+$50,189/呎
 (25年-12月-17日)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
         <is>
-          <t>B | 1506呎 (4+房)
+          <t>B | 1584呎 (4+房)
 $7800万
-$51,793/呎
+$49,242/呎
 (25年-11月-10日)</t>
         </is>
       </c>
@@ -6360,17 +6360,17 @@
       </c>
       <c r="B8" s="20" t="inlineStr">
         <is>
-          <t>A | 1506呎 (4+房)
+          <t>A | 1584呎 (4+房)
 $7600万
-$50,465/呎
+$47,980/呎
 (24年-08月-21日)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
         <is>
-          <t>B | 1506呎 (4+房)
+          <t>B | 1584呎 (4+房)
 $7400万
-$49,137/呎
+$46,717/呎
 (25年-03月-12日)</t>
         </is>
       </c>
@@ -6383,17 +6383,17 @@
       </c>
       <c r="B9" s="20" t="inlineStr">
         <is>
-          <t>A | 1508呎 (4+房)
+          <t>A | 1584呎 (4+房)
 $6950万
-$46,088/呎
+$43,876/呎
 (24年-11月-11日)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
         <is>
-          <t>B | 1508呎 (4+房)
+          <t>B | 1584呎 (4+房)
 $6880万
-$45,623/呎
+$43,434/呎
 (25年-07月-30日)</t>
         </is>
       </c>
@@ -6406,17 +6406,17 @@
       </c>
       <c r="B10" s="20" t="inlineStr">
         <is>
-          <t>A | 1508呎 (4+房)
+          <t>A | 1584呎 (4+房)
 $7398万
-$49,058/呎
+$46,705/呎
 (24年-01月-03日)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
         <is>
-          <t>B | 1508呎 (4+房)
+          <t>B | 1584呎 (4+房)
 $7200万
-$47,745/呎
+$45,455/呎
 (24年-05月-03日)</t>
         </is>
       </c>
@@ -6429,9 +6429,9 @@
       </c>
       <c r="B11" s="20" t="inlineStr">
         <is>
-          <t>A | 1508呎 (4+房)
+          <t>A | 1584呎 (4+房)
 $6750万
-$44,761/呎
+$42,614/呎
 (24年-01月-03日)</t>
         </is>
       </c>
@@ -6452,17 +6452,17 @@
       </c>
       <c r="B12" s="20" t="inlineStr">
         <is>
-          <t>A | 1508呎 (4+房)
+          <t>A | 1584呎 (4+房)
 $6500万
-$43,103/呎
+$41,035/呎
 (24年-05月-02日)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
         <is>
-          <t>B | 1508呎 (4+房)
+          <t>B | 1584呎 (4+房)
 $6850万
-$45,424/呎
+$43,245/呎
 (24年-04月-03日)</t>
         </is>
       </c>
@@ -6475,17 +6475,17 @@
       </c>
       <c r="B13" s="20" t="inlineStr">
         <is>
-          <t>A | 1508呎 (3房)
+          <t>A | 1584呎 (3房)
 $6340万
-$42,042/呎
+$40,025/呎
 (24年-03月-28日)</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
         <is>
-          <t>B | 1508呎 (3房)
+          <t>B | 1584呎 (3房)
 $6260万
-$41,512/呎
+$39,520/呎
 (24年-12月-16日)</t>
         </is>
       </c>
@@ -6498,17 +6498,17 @@
       </c>
       <c r="B14" s="20" t="inlineStr">
         <is>
-          <t>A | 1508呎 (3房)
+          <t>A | 1584呎 (3房)
 $6250万
-$41,446/呎
+$39,457/呎
 (24年-05月-21日)</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
         <is>
-          <t>B | 1508呎 (3房)
+          <t>B | 1584呎 (3房)
 $6180万
-$40,981/呎
+$39,015/呎
 (24年-11月-29日)</t>
         </is>
       </c>
@@ -6521,17 +6521,17 @@
       </c>
       <c r="B15" s="20" t="inlineStr">
         <is>
-          <t>A | 1508呎 (3房)
+          <t>A | 1584呎 (3房)
 $6120万
-$40,584/呎
+$38,636/呎
 (24年-04月-09日)</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
         <is>
-          <t>B | 1508呎 (3房)
+          <t>B | 1584呎 (3房)
 $6480万
-$42,971/呎
+$40,909/呎
 (25年-09月-22日)</t>
         </is>
       </c>
@@ -6544,17 +6544,17 @@
       </c>
       <c r="B16" s="20" t="inlineStr">
         <is>
-          <t>A | 1508呎 (3房)
+          <t>A | 1584呎 (3房)
 $6280万
-$41,645/呎
+$39,646/呎
 (24年-04月-03日)</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
         <is>
-          <t>B | 1508呎 (3房)
+          <t>B | 1584呎 (3房)
 $6200万
-$41,114/呎
+$39,141/呎
 (24年-04月-08日)</t>
         </is>
       </c>
@@ -6567,17 +6567,17 @@
       </c>
       <c r="B17" s="20" t="inlineStr">
         <is>
-          <t>A | 1438呎 (3房)
+          <t>A | 1515呎 (3房)
 $6580万
-$45,758/呎
+$43,432/呎
 (23年-12月-13日)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
         <is>
-          <t>B | 1438呎 (3房)
+          <t>B | 1515呎 (3房)
 $6450万
-$44,854/呎
+$42,574/呎
 (24年-04月-03日)</t>
         </is>
       </c>
@@ -6717,7 +6717,7 @@
       </c>
       <c r="B6" s="22" t="inlineStr">
         <is>
-          <t>A | 1507呎 (4+房)
+          <t>A | 1587呎 (4+房)
 -
 -
 (待售)</t>
@@ -6725,7 +6725,7 @@
       </c>
       <c r="C6" s="22" t="inlineStr">
         <is>
-          <t>B | 1505呎 (4+房)
+          <t>B | 1584呎 (4+房)
 -
 -
 (待售)</t>
@@ -6739,75 +6739,6 @@
         </is>
       </c>
       <c r="B7" s="22" t="inlineStr">
-        <is>
-          <t>A | 1547呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C7" s="22" t="inlineStr">
-        <is>
-          <t>B | 1506呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="58" customHeight="1">
-      <c r="A8" s="19" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B8" s="22" t="inlineStr">
-        <is>
-          <t>A | 1506呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C8" s="22" t="inlineStr">
-        <is>
-          <t>B | 1506呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="58" customHeight="1">
-      <c r="A9" s="19" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B9" s="22" t="inlineStr">
-        <is>
-          <t>A | 1508呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C9" s="22" t="inlineStr">
-        <is>
-          <t>B | 1508呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="58" customHeight="1">
-      <c r="A10" s="19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="B10" s="22" t="inlineStr">
         <is>
           <t>A | 1584呎 (4+房)
 -
@@ -6815,7 +6746,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C10" s="22" t="inlineStr">
+      <c r="C7" s="22" t="inlineStr">
         <is>
           <t>B | 1584呎 (4+房)
 -
@@ -6824,13 +6755,13 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="58" customHeight="1">
-      <c r="A11" s="19" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="B11" s="22" t="inlineStr">
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B8" s="22" t="inlineStr">
         <is>
           <t>A | 1584呎 (4+房)
 -
@@ -6838,7 +6769,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C11" s="22" t="inlineStr">
+      <c r="C8" s="22" t="inlineStr">
         <is>
           <t>B | 1584呎 (4+房)
 -
@@ -6847,46 +6778,115 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="58" customHeight="1">
-      <c r="A12" s="19" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B12" s="22" t="inlineStr">
-        <is>
-          <t>A | 1508呎 (4+房)
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B9" s="22" t="inlineStr">
+        <is>
+          <t>A | 1584呎 (4+房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="C12" s="22" t="inlineStr">
-        <is>
-          <t>B | 1508呎 (4+房)
+      <c r="C9" s="22" t="inlineStr">
+        <is>
+          <t>B | 1584呎 (4+房)
 -
 -
 (待售)</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="58" customHeight="1">
-      <c r="A13" s="19" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B13" s="22" t="inlineStr">
-        <is>
-          <t>A | 1508呎 (4+房)
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B10" s="22" t="inlineStr">
+        <is>
+          <t>A | 1584呎 (4+房)
 -
 -
 (待售)</t>
         </is>
       </c>
+      <c r="C10" s="22" t="inlineStr">
+        <is>
+          <t>B | 1584呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B11" s="22" t="inlineStr">
+        <is>
+          <t>A | 1584呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C11" s="22" t="inlineStr">
+        <is>
+          <t>B | 1584呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B12" s="22" t="inlineStr">
+        <is>
+          <t>A | 1584呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C12" s="22" t="inlineStr">
+        <is>
+          <t>B | 1584呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B13" s="22" t="inlineStr">
+        <is>
+          <t>A | 1584呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
       <c r="C13" s="22" t="inlineStr">
         <is>
-          <t>B | 1508呎 (4+房)
+          <t>B | 1584呎 (4+房)
 -
 -
 (待售)</t>
@@ -6909,7 +6909,7 @@
       </c>
       <c r="C14" s="22" t="inlineStr">
         <is>
-          <t>B | 1508呎 (3房)
+          <t>B | 1584呎 (3房)
 -
 -
 (待售)</t>
@@ -6924,7 +6924,7 @@
       </c>
       <c r="B15" s="22" t="inlineStr">
         <is>
-          <t>A | 1508呎 (3房)
+          <t>A | 1584呎 (3房)
 -
 -
 (待售)</t>
@@ -6932,7 +6932,7 @@
       </c>
       <c r="C15" s="22" t="inlineStr">
         <is>
-          <t>B | 1508呎 (3房)
+          <t>B | 1584呎 (3房)
 -
 -
 (待售)</t>
@@ -6947,7 +6947,7 @@
       </c>
       <c r="B16" s="22" t="inlineStr">
         <is>
-          <t>A | 1508呎 (3房)
+          <t>A | 1584呎 (3房)
 -
 -
 (待售)</t>
@@ -6955,7 +6955,7 @@
       </c>
       <c r="C16" s="22" t="inlineStr">
         <is>
-          <t>B | 1508呎 (3房)
+          <t>B | 1584呎 (3房)
 -
 -
 (待售)</t>
@@ -6970,17 +6970,17 @@
       </c>
       <c r="B17" s="20" t="inlineStr">
         <is>
-          <t>A | 1438呎 (3房)
+          <t>A | 1515呎 (3房)
 $6450万
-$44,854/呎
+$42,574/呎
 (24年-08月-12日)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
         <is>
-          <t>B | 1438呎 (3房)
+          <t>B | 1515呎 (3房)
 $6400万
-$44,506/呎
+$42,244/呎
 (24年-10月-30日)</t>
         </is>
       </c>
